--- a/files/AFL_upcoming_projections.xlsx
+++ b/files/AFL_upcoming_projections.xlsx
@@ -6,85 +6,324 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AFL JOINT Projections" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected / JOINT Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecast Rain mm</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date_local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_forecast_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_fallback_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scoring_environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_margin_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_total_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">margin_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state_as_of_round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_rating_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_coverage_scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment_uncapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projection_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_pts_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_line_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_total_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_total_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weather_rain_adjustment_reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_join_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_cold_starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optus Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interstate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hl16_k4_env36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_shock_career75_recent25_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_lean_v2_prod_fixed_hga_gmhba_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exact_date_and_teams</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">decay_0.975_lambda_100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbane lions</t>
   </si>
   <si>
     <t xml:space="preserve">adelaide crows</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gabba</t>
   </si>
   <si>
-    <t xml:space="preserve">No Rain</t>
+    <t xml:space="preserve">9030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -119,9 +358,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,23 +651,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="26.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="5.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -475,99 +698,1183 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+        <v>46276</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46276.7569444444</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-12.5</v>
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
       </c>
       <c r="I2" t="n">
-        <v>-15.6</v>
+        <v>3.25880377801953</v>
       </c>
       <c r="J2" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
+        <v>3.25880377801953</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.33193731775628</v>
       </c>
       <c r="L2" t="n">
-        <v>-21.5</v>
+        <v>-2.67451787319525</v>
       </c>
       <c r="M2" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
+        <v>180.777950834317</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-10.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>173.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.93394823616979</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.9610562429549</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.8153578785932</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.22167372028596</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>88.1859844357911</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>91.7582589516749</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>87.4716828001529</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.28657615152206</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>179.229941751828</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.275826053146547</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.00004259188128</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>178.367866635046</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.04536116623423</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.82383513563554</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6.33193731775628</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>180.777950834317</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>180.777950834317</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>92.0183773061682</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>88.7595735281486</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.0585609232072043</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.0585609232072043</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.702731078486452</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.275826053146547</v>
+      </c>
+      <c r="BQ2" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6.93460869982385</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-3.67580492180433</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>6.33193731775628</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ2" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46276.7569444444</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.33193731775628</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.67451787319525</v>
+      </c>
+      <c r="M3" t="n">
+        <v>181.053776887463</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="T3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.93394823616979</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.9610562429549</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10.8153578785932</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.22167372028596</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>88.1859844357911</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>91.7582589516749</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>87.4716828001529</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.28657615152206</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>179.229941751828</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.00004259188128</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>178.643692688193</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.04536116623423</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.82383513563554</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>6.33193731775628</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>181.053776887463</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>181.053776887463</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>92.1562903327414</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>88.8974865547219</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.25880377801953</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.0585609232072043</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.0585609232072043</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.702731078486452</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.275826053146547</v>
+      </c>
+      <c r="BQ3" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.93460869982385</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-3.67580492180433</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>6.33193731775628</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ3" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="B4" s="2" t="n">
+        <v>46277.8159722222</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12.5307407115642</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15.6336355157324</v>
+      </c>
+      <c r="M4" t="n">
+        <v>184.308552197688</v>
+      </c>
+      <c r="N4" t="n">
         <v>-21.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O4" t="n">
         <v>179.5</v>
       </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.7</v>
+      </c>
+      <c r="T4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.4343751412678</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5.83725634207668</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.784061390426256</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.50032074798573</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>88.1859844357911</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>99.9800388290732</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>90.3791793874415</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9.60085944163164</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>190.359218216515</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-5.59157959440939</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.1988459856892</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>181.898467998417</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.92988126993254</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.459086424417786</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>12.5307407115642</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>184.308552197688</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>184.308552197688</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>99.3390532001874</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>84.9694989975002</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.336639283273675</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.336639283273675</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-5.59157959440939</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>8.3510634053214</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>6.01849079736578</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>16.5704121108483</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46277.8159722222</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12.5307407115642</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15.6336355157324</v>
+      </c>
+      <c r="M5" t="n">
+        <v>189.900131792097</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T5" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15.4343751412678</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.83725634207668</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.784061390426256</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.50032074798573</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>88.1859844357911</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>99.9800388290732</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>90.3791793874415</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.60085944163164</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>190.359218216515</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.1988459856892</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>187.490047592826</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.92988126993254</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.459086424417786</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>12.5307407115642</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>189.900131792097</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>189.900131792097</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>102.134842997392</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>87.7652887947049</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14.3695542026872</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.336639283273675</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.336639283273675</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4.0396713992841</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-5.59157959440939</v>
+      </c>
+      <c r="BQ5" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>8.3510634053214</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>6.01849079736578</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>16.5704121108483</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ5" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_upcoming_projections.xlsx
+++ b/files/AFL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -62,10 +62,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
@@ -74,19 +74,10 @@
     <t xml:space="preserve">Weather Adjusted</t>
   </si>
   <si>
-    <t xml:space="preserve">SCG</t>
+    <t xml:space="preserve">MCG</t>
   </si>
   <si>
     <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCG</t>
   </si>
 </sst>
 </file>
@@ -423,7 +414,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -487,7 +478,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -505,25 +496,25 @@
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.2</v>
+        <v>-4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-17</v>
+        <v>-2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>185</v>
+        <v>190.7</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>188</v>
+        <v>185.5</v>
       </c>
       <c r="N2" t="s">
         <v>20</v>
@@ -534,7 +525,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -552,124 +543,30 @@
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.2</v>
+        <v>-4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-17</v>
+        <v>-2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>185</v>
+        <v>190.7</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>188</v>
+        <v>185.5</v>
       </c>
       <c r="N3" t="s">
         <v>20</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>190.7</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>190.7</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/AFL_upcoming_projections.xlsx
+++ b/files/AFL_upcoming_projections.xlsx
@@ -6,85 +6,324 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AFL JOINT Projections" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected / JOINT Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecast Rain mm</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date_local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_forecast_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_fallback_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scoring_environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_margin_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_total_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">margin_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state_as_of_round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_rating_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_coverage_scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment_uncapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projection_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_pts_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_line_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_total_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_total_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weather_rain_adjustment_reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_join_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_cold_starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interstate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hl16_k4_env36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_shock_career75_recent25_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_lean_v2_prod_fixed_hga_gmhba_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exact_date_and_teams</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">decay_0.975_lambda_100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
     <t xml:space="preserve">hawthorn</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane lions</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
     <t xml:space="preserve">MCG</t>
   </si>
   <si>
-    <t xml:space="preserve">No Rain</t>
+    <t xml:space="preserve">9027</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -119,9 +358,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,23 +651,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="26.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="5.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -475,99 +698,1183 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+        <v>46283</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46283.8194444444</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-4.7</v>
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5</v>
+        <v>9.24694053269745</v>
       </c>
       <c r="J2" t="n">
-        <v>190.7</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
+        <v>9.24694053269745</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11.2123806490855</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>16.9920715354185</v>
       </c>
       <c r="M2" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
+        <v>185.006009870469</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W2" t="n">
+        <v>14.3353730043783</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.87863999601354</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.35367969745155</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10.1995289112752</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>88.8956076517026</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>95.8914517448057</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>87.5605679502646</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8.33088379454111</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>183.45201969507</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.71749301267599</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>182.290832583403</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.8814968545444</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.55399017539872</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>11.2123806490855</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>185.006009870469</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>185.006009870469</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>97.1264752015832</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>87.8795346688858</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.55949426369001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.55949426369001</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>2.856329299604</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>6.39061123309345</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>17.9263118133656</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ2" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46283.8194444444</v>
+      </c>
+      <c r="C3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.2123806490855</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16.9920715354185</v>
+      </c>
+      <c r="M3" t="n">
+        <v>185.006009870469</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>188</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14.3353730043783</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.87863999601354</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.35367969745155</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10.1995289112752</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>88.8956076517026</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>95.8914517448057</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>87.5605679502646</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8.33088379454111</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>183.45201969507</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>9.71749301267599</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>182.290832583403</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.8814968545444</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.55399017539872</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>11.2123806490855</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>185.006009870469</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>185.006009870469</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>97.1264752015832</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>87.8795346688858</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.24694053269745</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.55949426369001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.55949426369001</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>6.71393116428012</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>2.856329299604</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>6.39061123309345</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>17.9263118133656</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46284</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>190.7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="B4" s="2" t="n">
+        <v>46284.71875</v>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.46420498358476</v>
+      </c>
+      <c r="M4" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O4" t="n">
         <v>185.5</v>
       </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.78914393266532</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.9389492981768</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.03530566564961</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.823450077597943</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>88.8956076517026</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>96.72130150677</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>93.9392512842298</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.78205022254021</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>190.660552791</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.24510031170556</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>188.020696722436</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.95793772557488</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.0753212185018644</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>95.3958954775736</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>95.339978531928</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.0577846075606759</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.0577846075606759</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0.693415290728111</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2.51108142560716</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-2.45516447996155</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46284.71875</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.46420498358476</v>
+      </c>
+      <c r="M5" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.78914393266532</v>
+      </c>
+      <c r="X5" t="n">
+        <v>16.9389492981768</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.03530566564961</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.823450077597943</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>88.8956076517026</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>96.72130150677</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>93.9392512842298</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.78205022254021</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>190.660552791</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.24510031170556</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>188.020696722436</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.95793772557488</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.0753212185018644</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>190.735874009502</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>95.3958954775736</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>95.339978531928</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.0559169456456097</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.0577846075606759</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.0577846075606759</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.693415290728111</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2.51108142560716</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-2.45516447996155</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>4.73998794811508</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_upcoming_projections.xlsx
+++ b/files/AFL_upcoming_projections.xlsx
@@ -6,75 +6,300 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AFL JOINT Projections" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected / JOINT Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecast Rain mm</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date_local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tab_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_forecast_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_fallback_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scoring_environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_margin_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_total_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rain_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_pre_intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">margin_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_calibration_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_margin_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_total_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state_as_of_round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_rating_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_pred_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pred_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_feature_coverage_scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_changes_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_players_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_adjustment_cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_margin_adjustment_uncapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projection_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_pts_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_line_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_delta_total_raw_selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_total_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weather_rain_adjustment_reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_join_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_cold_starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_config_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hl16_k4_env36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_shock_career75_recent25_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afl_lean_v2_prod_fixed_hga_gmhba_fixed12_gate3_cap8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exact_date_and_teams</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCG</t>
+    <t xml:space="preserve">decay_0.975_lambda_100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
   </si>
   <si>
     <t xml:space="preserve">No Rain</t>
@@ -84,7 +309,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -119,9 +346,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,23 +639,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="26.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="5.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -474,100 +685,694 @@
       </c>
       <c r="O1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46291</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+      <c r="B2" s="2" t="n">
+        <v>46291.6041666667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3</v>
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
       </c>
       <c r="I2" t="n">
-        <v>18.3</v>
+        <v>-8.05915812475158</v>
       </c>
       <c r="J2" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.298990761306082</v>
       </c>
       <c r="L2" t="n">
+        <v>-18.2938112480403</v>
+      </c>
+      <c r="M2" t="n">
+        <v>180.102714268405</v>
+      </c>
+      <c r="N2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>185.5</v>
       </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" t="n">
-        <v>13.7</v>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5.5783118332481</v>
+      </c>
+      <c r="X2" t="n">
+        <v>18.3229660636695</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.1038815720235</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.210184302147481</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>89.2104829685578</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>94.9989791039534</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>96.4295674602038</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.43058835625042</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>191.428546564157</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-11.4776754487624</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1.66869838767747</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>177.282657566039</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.13159759494434</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.151843153010011</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.298990761306082</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>180.102714268405</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>180.102714268405</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>86.0217780718267</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>94.0809361965782</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.19893923440237</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.19893923440237</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-2.38727081282844</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-11.4776754487624</v>
+      </c>
+      <c r="BQ2" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.85829274809475</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-12.9174508728463</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-0.298990761306082</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ2" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>46291</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="B3" s="2" t="n">
+        <v>46291.6041666667</v>
+      </c>
+      <c r="C3" t="n">
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3</v>
+        <v>83</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
       </c>
       <c r="I3" t="n">
-        <v>18.3</v>
+        <v>-8.05915812475158</v>
       </c>
       <c r="J3" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.298990761306082</v>
       </c>
       <c r="L3" t="n">
+        <v>-18.2938112480403</v>
+      </c>
+      <c r="M3" t="n">
+        <v>191.580389717167</v>
+      </c>
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>185.5</v>
       </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="n">
-        <v>13.7</v>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="T3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.5783118332481</v>
+      </c>
+      <c r="X3" t="n">
+        <v>18.3229660636695</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11.1038815720235</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.210184302147481</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>89.2104829685578</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>94.9989791039534</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>96.4295674602038</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.43058835625042</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>191.428546564157</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-1.66869838767747</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>188.760333014801</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.13159759494434</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.151843153010011</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.298990761306082</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>191.580389717167</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>191.580389717167</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>91.7606157962078</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>99.8197739209594</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-8.05915812475158</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.19893923440237</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.19893923440237</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-2.38727081282844</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-11.4776754487624</v>
+      </c>
+      <c r="BQ3" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.85829274809475</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-12.9174508728463</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-0.298990761306082</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ3" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>
